--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -491,6 +491,384 @@
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jerarquía inconsistente: la primera línea de la Parte 4.2 arrastra una viñeta '1.' que el resto del documento no usa.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Auditoría interna del Markdown (Análisis 4.2).</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Se aplica el encabezado no numerado `{-}` (pandoc) en la línea 1; el contenido no cambia (T1).</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>04_arquitectura/entrega_2/texto/arquitectura_fisica.md (línea 1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>El proyecto LaTeX del Subdocumento 4.2 no tiene evidencia de compilación ni verificación completa de las fuentes.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Auditoría interna del proyecto LaTeX.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 (LaTeX)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Se revisa el armado completo (main.tex, contenido.tex, latexmkrc, lafrox-portada.tex) y se confirma la instrucción: latexmk main.tex con LuaLaTeX ($pdf_mode = 4). El entorno actual no tiene distribución TeX, así que el PDF no se produce en esta máquina (T2).</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SUBDOCUMENTO_4/Subdocumento_4_LateX (README.md, main.tex, contenido.tex)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Parcial — sin compilar (sin TeX instalado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Restos de texto basura ('LAFROX/SUBDOCUMENTO 5…') quedaron pegados al final del Markdown.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Auditoría interna del Markdown.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Se elimina el bloque basura; la estructura de secciones queda verificada intacta (15 ADR-01…15, secciones correctas).</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>arquitectura_fisica.md (final del documento)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Verificar que las referencias al modelo de emplazamiento híbrido apunten a rutas válidas.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Auditoría interna de diagramas.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Verificación únicamente: la ruta y el archivo ARQF-01_Modelo_emplazamiento_hibrido.png existen en Diagramas/; no se modificó arte (T4).</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Modelo de emplazamiento híbrido (figuras del LaTeX y referencias del md)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Párrafos extensos (varios por subsección) se leen mejor como viñetas en un documento de oferta.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Auditoría interna de legibilidad (Informe 2 / T-22).</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Se convierten ~74 fragmentos a viñetas en Markdown y a itemize en LaTeX: inicio (01 a 08_g), integración (09_h), seguridad (10_i), despliegue (11_j), dimensionamiento (12_k), capa analítica (13_l) y ADR (14_m) (T5).</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>partes/01_vision_general …08_g, 09_h, 10_i, 11_j, 12_k, 13_l, 14_m (.tex) y secciones análogas del md</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Citas de requisitos (RT-xx.yy) que quedaron entre paréntesis sin glosa.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Auditoría interna de citas normativas.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Auditoría conservadora: no se elimina ningún paréntesis normativo; todos responden a requisitos citables y se dejan tal cual (T6).</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>La Política de sesión (Art. 22) está redactada como párrafo único sin desglosar RT-12.07 / RT-12.08.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bases Técnicas Transversales (RT-12.07, RT-12.08, RT-12.12).</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Se reescribe la subsección 4.4 en cinco viñetas (duración, caducidad, renovación, revocación y sesiones concurrentes) más elevación temporal de privilegios, con la referencia a Art. 22 · RT-12.07 · RT-12.08. Se anota que la planilla de la Tabla 48 cita RT-12.12 donde md/tex citan RT-12.08 (T7).</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10_i_seguridad.tex (4.4 Política de sesión) y md (sección 4.4 / Tabla 48)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Los conteos '· N filas' de los punteros del Markdown no coinciden con las planillas (desfase sistemático de +1); seis tablas de dos columnas se leen mejor como viñetas.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Auditoría de planillas (.xlsx) vs. punteros del md y tablalafrox del LaTeX.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Se corrigen los 115 punteros del md a N-1 (iguales a las filas reales de la planilla y a las del LaTeX; '1 fila' en singular). Se convierten a viñetas 6 tablas etiqueta→definición (t33, t37 en 09_h; t47, t49, t50, t52 en 10_i), conservando el puntero hacia la planilla; las matrices con datos se mantienen como tablas (T8).</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>arquitectura_fisica.md (punteros de tablas) y partes/09_h, partes/10_i</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Verificación final de coherencia entre Markdown canónico y LaTeX, y registro de los cambios en la trazabilidad T-22.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cierre de la auditoría de la Parte 4.2.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Verificados: itemize balanceados en 09_h (6/6) y 10_i (12/12); 0 referencias \ref a tablas convertidas; estructura del md intacta; conteo de tablas del LaTeX actualizado a 112; registro en esta planilla (T9).</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Verificada</t>
         </is>
       </c>
     </row>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -869,6 +869,48 @@
       <c r="H12" t="inlineStr">
         <is>
           <t>Verificada</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Auditoría de sobresolución (sobre-dimensionamiento) en la Parte 4.2: ancho de banda WAN (12.2.3 / Tabla 81) y otros puntos de dimensionamiento.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Solicitud interna de revisión del dimensionamiento (RT-03.20 vs. RT-09.03).</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Se audita toda la Parte (k): cómputo, almacenamiento, TPS y WAN quedan alineados al crecimiento 3× sin rediseño que exige RT-09.03 (obligatorio), por lo que NO se reduce capacidad. Se corrige la justificación de ancho de banda (régimen por sincronización de flota en ventana de retorno ≈4–5 Mbps a 3× más evidencia/DTE ≈1–2 Mbps; peak por respaldo semanal ≈40→120 GB ≈40 Mbps) que antes no derivaba los 20→50/10→20 Mbps (RT-03.20), y se re-da el SLA de sincronización de flota a ventana 17:00–20:00 por lotes de ≤10 min (compatible con el enlace a 3×). Se elimina el rótulo "continúa en la página siguiente" y se pasa la numeración de tablas/figuras a contador continuo (Tabla 1, 2, …).</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>12_k_dimensionamiento.tex (14.2 ancho de banda, t81 + justificación, t77/t83 notas), 04_c_implementos.tex C10, lafrox.cls (endfoot), main.tex (thetable/thefigure), listas de tablas y figuras</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Atendida</t>
         </is>
       </c>
     </row>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R6057c451c6214cc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Re296eeb6affb499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="Rb9d7b4183f5a45a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R384a1b08a6174afa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -857,6 +857,32 @@
         <x:v>Parcial: preliminar incorporado; revisión técnica pendiente</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="165" customHeight="1">
+      <x:c r="A15" s="4" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="str">
+        <x:v>Integrar la revisión 67 de arquitectura lógica y mejorar claridad y coherencia del subdocumento 4.1.</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="str">
+        <x:v>Solicitud de Álvaro; arquitectura_logica_version67.md, revisión 67.</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="str">
+        <x:v>Subdoc 4.1 (arquitectura lógica)</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="str">
+        <x:v>Se actualizan Markdown y LaTeX: ACL exclusiva del ERP, hub EDI, datos offline, identidad, roles de sitio y observabilidad. Se corrigen autonomía mínima, flujos de acceso y garantías no demostradas. Arquitectura física y Entrega 1 intactas.</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="str">
+        <x:v>4.1–4.7; 04_arquitectura/entrega_2/texto/arquitectura_logica.md y latex/subdoc_4.1.tex; README de revisión.</x:v>
+      </x:c>
+      <x:c r="G15" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H15" s="4" t="str">
+        <x:v>Parcial: integración editorial terminada; identidad offline, matriz de roles, DR y concordancia gráfica pendientes de validación.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="Rb9d7b4183f5a45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R384a1b08a6174afa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R60e344679bed4999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rc2bfba8e57f041ca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -883,6 +883,32 @@
         <x:v>Parcial: integración editorial terminada; identidad offline, matriz de roles, DR y concordancia gráfica pendientes de validación.</x:v>
       </x:c>
     </x:row>
+    <x:row r="16" ht="165" customHeight="1">
+      <x:c r="A16" s="4" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="str">
+        <x:v>Unificar la redacción de arquitectura lógica y retirar referencias editoriales a versiones y modificaciones.</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="str">
+        <x:v>Solicitud de Álvaro del 22-09-2026 y archivo LaTeX editado por el usuario.</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="str">
+        <x:v>Subdoc 4.1 (arquitectura lógica)</x:v>
+      </x:c>
+      <x:c r="E16" s="4" t="str">
+        <x:v>Se depuran texto y portada. Se aclaran perfiles y permisos, idempotencia en servicios de negocio, acceso local sin Gateway remoto y atributos del lote. Se mantiene Django y se explicitan las condiciones de aceptación del acceso desconectado.</x:v>
+      </x:c>
+      <x:c r="F16" s="4" t="str">
+        <x:v>Secciones 4.1–4.7 y portada del subdocumento 4.1.</x:v>
+      </x:c>
+      <x:c r="G16" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H16" s="4" t="str">
+        <x:v>Limpieza editorial completada. La autorización de relevos sin IdP y la concordancia de los diagramas requieren validación técnica.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Observaciones Informe 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -909,6 +909,48 @@
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>El Markdown de la Parte 4.2 (entrega_2) quedó desalineado del LaTeX, que es la versión que manda: estructura, recortes de seguridad, tablas y cifras distintas.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Auditoría interna de coherencia Markdown vs. LaTeX.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Se regenera el md completo desde las partes vigentes del LaTeX (contenido.tex: 01, 02, 03, 04, 05, 06, 09, 10, 11, 12, 14), sin corregir contenido. Las tablas pasan de punteros a planilla a tablas en línea, porque las planillas .xlsx de entrega_2 están desactualizadas (tri-camino WAN, AMP/Grafana, TIER II). Operación desconectada queda dentro de Emplazamiento, como en el LaTeX.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>04_arquitectura/entrega_2/texto/arquitectura_fisica.md (documento completo)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Atendida</t>
         </is>
@@ -938,9 +980,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -961,9 +1000,6 @@
           <t>tabla de trazabilidad observación–respuesta–sección modificada.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R60e344679bed4999"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rc2bfba8e57f041ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R4ada3191f3054ff8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rfcd304ad1d3b4081"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -909,6 +909,162 @@
         <x:v>Limpieza editorial completada. La autorización de relevos sin IdP y la concordancia de los diagramas requieren validación técnica.</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="108" customHeight="1">
+      <x:c r="A17" s="4" t="str">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="str">
+        <x:v>Diagramas del 4.1 ilegibles, repetidos y desconectados de la explicación; falta secuencia del pedido y modelo de dominio.</x:v>
+      </x:c>
+      <x:c r="C17" s="4" t="str">
+        <x:v>Revisión del evaluador, Subdocumento 4.1, pp. 9-10.</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="str">
+        <x:v>Subdoc 4.1</x:v>
+      </x:c>
+      <x:c r="E17" s="4" t="str">
+        <x:v>Se sustituyen las vistas repetitivas e ilegibles del cuerpo por una vista general legible y cuatro diagramas específicos: pedido con conexión, pedido sin conexión, acceso local y dominio. Los originales se conservan en la biblioteca. Cada figura nueva se cita y analiza en su sección.</x:v>
+      </x:c>
+      <x:c r="F17" s="4" t="str">
+        <x:v>4.1, Capas 2-5; Modelo de datos conceptual; diagramas ARQL-15 a ARQL-19.</x:v>
+      </x:c>
+      <x:c r="G17" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H17" s="4" t="str">
+        <x:v>Atendida en texto; pendiente revisión visual del PDF compilado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="108" customHeight="1">
+      <x:c r="A18" s="4" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="str">
+        <x:v>No se identifican los doce módulos con actor, interfaces y etapa ni se muestra requerimiento a módulo y capa.</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="str">
+        <x:v>Revisión del evaluador, Subdocumento 4.1, pp. 9-10.</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="str">
+        <x:v>Subdoc 4.1</x:v>
+      </x:c>
+      <x:c r="E18" s="4" t="str">
+        <x:v>Se completa la tabla de M1-M12 con actor y etapa y se agrega trazabilidad RF-módulo-capa con evidencia; se mantiene el detalle exhaustivo como responsabilidad del Formulario T-12.</x:v>
+      </x:c>
+      <x:c r="F18" s="4" t="str">
+        <x:v>4.1, Módulos funcionales y límites de contexto; Tablas de módulos y trazabilidad lógica.</x:v>
+      </x:c>
+      <x:c r="G18" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H18" s="4" t="str">
+        <x:v>Atendida en 4.1; contrastar contra T-12 consolidado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="108" customHeight="1">
+      <x:c r="A19" s="4" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="str">
+        <x:v>Identidad de ocho horas y puerta de enlace remota no explican dos relevos ni el trabajo de 120 terminales durante 24 horas sin nube.</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="str">
+        <x:v>Revisión del evaluador, Subdocumento 4.1, p. 10; consistencia transversal, p. 17.</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="str">
+        <x:v>Subdoc 4.1</x:v>
+      </x:c>
+      <x:c r="E19" s="4" t="str">
+        <x:v>Se define manifiesto firmado renovado cada hora, verificador de turno y puerta de API local con controles de esquema, tasa, autorización y auditoría. La prueba parte antes de dos relevos y reconoce el límite de revocación remota.</x:v>
+      </x:c>
+      <x:c r="F19" s="4" t="str">
+        <x:v>4.1, Capas 3 y 7; Figura de acceso local; funciones sin conexión.</x:v>
+      </x:c>
+      <x:c r="G19" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H19" s="4" t="str">
+        <x:v>Diseño lógico atendido; prueba de 24 h pendiente</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="108" customHeight="1">
+      <x:c r="A20" s="4" t="str">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="str">
+        <x:v>No se demuestra aplicación de SOLID, orquestación/coreografía ni cobertura de los cinco ambientes del SDLC.</x:v>
+      </x:c>
+      <x:c r="C20" s="4" t="str">
+        <x:v>Revisión del evaluador, Subdocumento 4.1, pp. 9-10.</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="str">
+        <x:v>Subdoc 4.1</x:v>
+      </x:c>
+      <x:c r="E20" s="4" t="str">
+        <x:v>Se sitúan los cinco principios en contratos concretos, se distingue confirmación síncrona de reacción por eventos y se especifica qué se prueba y promueve en Desarrollo, QA, Preproducción, Producción y DR.</x:v>
+      </x:c>
+      <x:c r="F20" s="4" t="str">
+        <x:v>4.1, Integración y eventos; Ambientes del ciclo de vida; Patrones de diseño.</x:v>
+      </x:c>
+      <x:c r="G20" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H20" s="4" t="str">
+        <x:v>Atendida en diseño; verificar topología con 4.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="108" customHeight="1">
+      <x:c r="A21" s="4" t="str">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="str">
+        <x:v>La decisión sobre excursión térmica difiere entre 3 y 4.1; el conductor no debe liberar un lote.</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="str">
+        <x:v>Revisión del evaluador, Subdocumentos 3 y 4.1, pp. 8 y 10.</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="str">
+        <x:v>Subdoc 4.1</x:v>
+      </x:c>
+      <x:c r="E21" s="4" t="str">
+        <x:v>Se fija retención preventiva automática local en M9/M5 y liberación exclusiva por Calidad, con registro de umbral, lote, causa y autoridad. El conductor solo informa y conserva la carga.</x:v>
+      </x:c>
+      <x:c r="F21" s="4" t="str">
+        <x:v>4.1, M9 Calidad; Integración y eventos; Reglas de reconciliación.</x:v>
+      </x:c>
+      <x:c r="G21" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H21" s="4" t="str">
+        <x:v>4.1 atendido; falta armonizar Subdoc 3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="108" customHeight="1">
+      <x:c r="A22" s="4" t="str">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="str">
+        <x:v>La comparación de alternativas es superficial y remite a un ADR alojado en 4.2 que incluye precios.</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="str">
+        <x:v>Revisión del evaluador, Subdocumento 4.1, p. 10; observación 4.2, p. 13.</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="str">
+        <x:v>Subdoc 4.1</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="str">
+        <x:v>Se hace autocontenido el registro lógico con alternativa, criterio y consecuencia de siete decisiones, y se eliminan las referencias a un adjunto inexistente. Las elecciones tecnológicas se explican por su función en Puelche.</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="str">
+        <x:v>4.1, Tecnologías seleccionadas; Registro de decisiones; Comparación de alternativas.</x:v>
+      </x:c>
+      <x:c r="G22" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H22" s="4" t="str">
+        <x:v>Atendida en 4.1; revisión humana pendiente</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -953,6 +953,174 @@
       <c r="H14" t="inlineStr">
         <is>
           <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cobertura de los ambientes del SDLC en una sola línea: no se describe DEV, QA, PREPROD ni PROD, ni qué se despliega en cada uno (S4.1). Anuncia cinco ambientes y lista seis (S1).</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Revisión del Informe 1 — Subdocumentos 4.1 y 1.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 (y 4.1, 1)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Se fija la lista única de las Bases (definición de AMBIENTE en las Administrativas y numeral 4.1 de las Transversales): Desarrollo, QA, Preproducción, Producción y Recuperación ante Desastres. Un cambio recorre tres ambientes antes de Producción. La marcha blanca se ubica en Producción (definición de MARCHA BLANCA). Se agregan las exigencias por ambiente (Desarrollo reconstruible desde código; QA con datos versionados y reinicio a estado conocido; RT-11.25), el apagado fuera de horario de los tres no productivos (RT-15.02, RT-04.13) y las tres diferencias declaradas de Preproducción frente a Producción, incluido el sitio on-premise emulado sin túnel a las bodegas (RT-04.02). La recuperación ante desastres se declara en dos dominios: us-east-1 para la nube y el CD Concepción para el on-premise. Pendiente: columna «qué se despliega» por ambiente, párrafo de remisión en el 4.1 y lista única en el Subdocumento 1.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SUBDOCUMENTO_4/.../partes/11_j_despliegue.tex (4.2.3 Ambientes y ciclo de entrega, Tabla t62) y 04_arquitectura/entrega_2/texto/arquitectura_fisica.md (Ambientes de despliegue, Tabla 62)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Faltan el diagrama de red y el diagrama de despliegue por ambiente (S4.2, «Qué se espera en el Informe 2»).</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Revisión del Informe 1 — Subdocumento 4.2.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Se define el conjunto de figuras de la vista de despliegue (RT-02.03): Producción a página completa (sa-east-1, Talca, Concepción y cross-docking), Recuperación ante Desastres (us-east-1 y Concepción), Desarrollo/QA/Preproducción en una figura comparativa con la tabla de diferencias de RT-04.02, y flujo de promoción del artefacto (RT-04.08). Aún no dibujadas.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4.2.3 Arquitectura de despliegue (11_j_despliegue.tex)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>No hay plano de distribución del recinto (RT-06.03) y la sala de ≈ 173 m² está sobredimensionada para una sala técnica secundaria (S4.2 d).</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Revisión del Informe 1 — Subdocumento 4.2.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Subdoc 4.3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Borrador de la Figura 4.3-1 en dos partes: (a) zonas y tres líneas de acceso con las siete zonas de RT-06.03 y RT-06.20 a 06.24, dimensionado a sala secundaria (numeral 6.1); (b) plano con medidas, por corregir (UPS en recinto propio, zona de trabajo fuera de la sala de servidores, esclusa, extinción RT-06.16/06.17 y superficie recalculada). Decisión asociada: los equipos del operador (ONT y router LTE) pasan a la acometida de comunicaciones de la 2.ª línea para que el proveedor no cruce la 3.ª línea.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>05_d_sitio_principal.tex (Figura 4.3-1)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>No hay diagrama de racks (RT-06.05) (S4.2 d).</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Revisión del Informe 1 — Subdocumento 4.2.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Subdoc 4.3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Borrador de la Figura 4.3-2: R01 servidores y R02 comunicaciones separados, ocupación U por U con paneles, organizadores, KVM y ODF, kW por rack y PDU A/B; el margen de crecimiento se declara eléctrico (crecimiento vertical), no de espacio. Pendiente: decidir 42U o 24U (numeral 6.1), ajustar T-11 C8 (paneles también en R01) y declarar las alturas en U de NAS, firewalls, switches y KVM.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>05_d_sitio_principal.tex (Figura 4.3-2) y Formulario T-11 (D11, C8)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1121,6 +1121,48 @@
       <c r="H18" t="inlineStr">
         <is>
           <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tablas con columnas tan angostas que parten las palabras y dejan los identificadores cortados (General, Prolijidad y formateo).</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Revisión del Informe 1 — General.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 (LaTeX)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Se compila el subdocumento con LuaLaTeX (MiKTeX) y se revisa el PDF completo: tamaño carta, cuerpo de 11 pt, folio y media firma en cada página, sin referencias rotas. En el Anexo 4.A (Formulario T-11) se impide el corte en guiones explícitos, de modo que ningún código (RT-02.11, cross-docking) queda partido entre líneas; se ensancha la Tabla 2 para que el encabezado «On-premise» no desborde. Pendiente: páginas semivacías del anexo por filas muy altas (se propone entregar el T-11 como archivo propio), portada que cita solo la parte 4.2 y los Formularios T-7 y T-21, y página de apertura de la parte casi vacía.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>04_arquitectura_fisica/contenido.tex (anexo), partes/02_a_emplazamiento.tex (Tabla 2)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Parcial</t>
         </is>
       </c>
     </row>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R4ada3191f3054ff8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rfcd304ad1d3b4081"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R9666066b2813431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rb614f52b84e34385"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1065,6 +1065,32 @@
         <x:v>Atendida en 4.1; revisión humana pendiente</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="108" customHeight="1">
+      <x:c r="A23" s="4" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="str">
+        <x:v>La elección de Django para el backend ya no representa la plataforma acordada para la arquitectura lógica; se requiere conservar contratos, datos y operación offline al adoptar Laravel.</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="str">
+        <x:v>Solicitud de Álvaro, 25-09-2026; contraste de 4.1 con la rama Guillermo-subdoc4-consistencia.</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="str">
+        <x:v>Subdoc 4.1 (arquitectura lógica)</x:v>
+      </x:c>
+      <x:c r="E23" s="4" t="str">
+        <x:v>Se define Laravel 13/PHP 8.5 en M1--M12, límites PSR-4, persistencia PostGIS, Keycloak OIDC, consumidor JSON de SQS separado de trabajos Laravel, adaptador RabbitMQ, pruebas y transición por sitio con escritor único y reversión.</x:v>
+      </x:c>
+      <x:c r="F23" s="4" t="str">
+        <x:v>4.1.1 Tecnologías; Capa 4; Capa 5; Capa 7; Detalle de tecnologías; Implantación progresiva; ADR-01/05/12; Alternativas.</x:v>
+      </x:c>
+      <x:c r="G23" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H23" s="4" t="str">
+        <x:v>Atendida en 4.1; 4.2, T-11 y ADR físicos pendientes de armonización</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1163,6 +1163,132 @@
       <c r="H19" t="inlineStr">
         <is>
           <t>Parcial</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Consistencia técnica entre subdocumentos: la arquitectura lógica (4.1) adoptó Laravel 13 / PHP 8.5 (origin/arquitectura-alvaro, commit ad60c0c) y la física seguía declarando Django, workers Celery y celery-erp-sync; la revisión del Informe 1 sanciona las contradicciones entre subdocumentos (Consideraciones transversales; aclaración 7.1 c).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Revisión del Informe 1 — Consideraciones transversales; cambio de framework del 4.1.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2, 4.3 y Formulario T-11</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Se alinea la arquitectura física con Laravel sin reemplazo literal: perfiles de ejecución (API y wms_only con PHP-FPM; shipper, consumidor de reconciliación, trabajos y planificador en PHP CLI) con arranque, salud y terminación ordenada; cola SQS FIFO de reconciliación con sobre JSON versionado separada de las colas de trabajos Laravel; erp-sync con clave idempotente; réplica DMS separada de la aplicación de eventos, con clave de origen única; RPO remoto del WMS solo con enlace y registro retenido de 24 h; dimensionamiento PHP recalculado con supuestos declarados (condición de aceptación); CI con Composer, PHPUnit, PHPStan/Larastan, Pint y contratos OpenAPI/AsyncAPI; OpenTelemetry PHP; motor de rutas y AS2 (AWS Transfer Family) aislados tras contrato versionado. ADR-01, 05, 11, 12 y 14 reformulados en estado propuesta; ADR-04, 06, 08 y 13 ajustados. Se alinean también arquitectura_fisica.md, Arquitectura/fisica (ADR v01, Tabla de emplazamiento v06, T-11, T-12) y siete planillas. Pendiente: prueba de carga que confirme tareas y procesos, selección del motor VRP (&lt; 20 min) e interoperabilidad AS2 por cadena; aprobación de los ADR en propuesta.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>02_a_emplazamiento.tex (4.2.1), 02_b_servicios_nube.tex (4.2.2), 11_j_despliegue.tex (4.2.3: perfiles, transición, réplica y observabilidad), 02_c_conexiones.tex (4.2.4), 12_k_dimensionamiento.tex (4.2.5), 04_c_implementos.tex (4.2.6), 05_d y 06_e (4.3), 14_m_decisiones_adr.tex, 15_anexo_t11.tex (Formulario T-11)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Los formularios deben entregarse como archivo propio (aclaraciones, sección 1) y el merge 9c0b760 dejó el subdocumento sin compilar al llamar a partes/15_anexo_t11.tex, que el renombre del Formulario T-11 había retirado.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Aclaraciones de la licitación, sección 1; revisión interna de compilación.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Subdoc 4 y Formulario T-11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>El cuerpo del Formulario T-11 queda en una fuente única (partes/15_anexo_t11.tex) que usan el subdocumento, al final y de forma provisoria, y LAFROX-Formulario-T-11.tex como archivo propio. Ambos compilan. Para la entrega basta comentar la línea \parte del anexo en contenido.tex.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>04_arquitectura_fisica/contenido.tex; partes/15_anexo_t11.tex; LAFROX-Formulario-T-11.tex</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Formato del apartado 4.2: el título se imprimía como «Capítulo 4.2», la «Visión general» era un capítulo sin numerar ajeno al índice obligatorio y cada tabla y figura llevaba la leyenda «Fuente: elaboración propia», que la aclaración 7.1 a) cita como indicio de redacción por IA.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Revisión interna de forma; aclaraciones, secciones 2 y 7.1.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 y 4.3</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>El título de cada apartado se imprime como «4.2 Arquitectura física» (y 4.3, 4.4) sin el rótulo «Capítulo»; la visión general pasa a ser la introducción de 4.2; se retiran todas las líneas de fuente bajo tablas y figuras (39) y las leyendas de las figuras 4.3-1 y 4.3-2. Las referencias al caso y a las Bases se mantienen dentro del texto.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>contenido.tex (formato de título); partes/02_0_arquitectura_fisica.tex (introducción); partes/01_vision_general.tex (retirado); partes 02_a, 02_b, 02_c, 04_c, 05_d, 06_e, 11_j y 12_k</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Resuelta</t>
         </is>
       </c>
     </row>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R9666066b2813431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rb614f52b84e34385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="Rc4877283625f4917"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rb8f08f3eb8e1460e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -49,7 +49,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyAlignment="1">
@@ -60,6 +60,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1091,6 +1094,110 @@
         <x:v>Atendida en 4.1; 4.2, T-11 y ADR físicos pendientes de armonización</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="108" customHeight="1">
+      <x:c r="A24" s="4" t="str">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B24" s="4" t="str">
+        <x:v>Las tablas extensas del Subdocumento 4.1 se parten entre páginas o desplazan el análisis del cuerpo principal.</x:v>
+      </x:c>
+      <x:c r="C24" s="4" t="str">
+        <x:v>Bases/aclaraciones-licitacion.md, sección 5; revisión de paginación de 4.1.</x:v>
+      </x:c>
+      <x:c r="D24" s="4" t="str">
+        <x:v>Subdoc 4.1 (arquitectura lógica)</x:v>
+      </x:c>
+      <x:c r="E24" s="4" t="str">
+        <x:v>Se trasladan doce catálogos y matrices extensas a los anexos 4.1-A a 4.1-L. El cuerpo conserva síntesis, análisis y citas expresas al anexo correspondiente.</x:v>
+      </x:c>
+      <x:c r="F24" s="4" t="str">
+        <x:v>4.1, eventos, gobierno, carga masiva, módulos, trazabilidad, límites de contexto, interfaces, volumen, continuidad offline, reconciliación y decisiones del caso; anexos 4.1-A a 4.1-L.</x:v>
+      </x:c>
+      <x:c r="G24" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H24" s="4" t="str">
+        <x:v>Atendida en 4.1; compilación y revisión visual pendientes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="108" customHeight="1">
+      <x:c r="A25" s="4" t="str">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B25" s="4" t="str">
+        <x:v>La vista general de arquitectura lógica aún mostraba el stack anterior y el archivo de anexos no encontraba la plantilla al abrirse desde su carpeta.</x:v>
+      </x:c>
+      <x:c r="C25" s="4" t="str">
+        <x:v>Revisión del Subdocumento 4.1 y solicitud de Álvaro, 26-09-2026.</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="str">
+        <x:v>Subdoc 4.1 (arquitectura lógica)</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="str">
+        <x:v>Se corrigió la ruta de la clase y la portada del archivo de anexos; se compiló su PDF. Se recreó el diagrama general con Laravel/PHP, se actualizó la figura resumida del 4.1 y se verificó su legibilidad impresa.</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="str">
+        <x:v>4.1, Figura 4.1; Diagramas/arquitectura_logica_actual/ARQL-19 y ARQL-20; anexos_4.1.tex y anexos_4.1.pdf.</x:v>
+      </x:c>
+      <x:c r="G25" s="4" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H25" s="4" t="str">
+        <x:v>Atendida en 4.1; revisión humana del consolidado pendiente</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="108" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>Integrar las vistas Laravel y descripciones elaboradas en paralelo, preservando los cambios locales del 4.1.</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Solicitud de Álvaro; aporte de Tomás, commit b08b623.</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>Subdoc 4.1: diagramas y vistas por actor</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>Se integraron 14 PNG, TXT y capa de negocio. Se precisaron las descripciones del conductor externo y de TI; se documentaron diferencias de TTL, acceso HHT y etiqueta residual antes de sustituir figuras consolidadas.</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>Diagramas/arquitectura_logica_actual/cambios laravel/LECTURA_DIAGRAMAS.md y capas/04_negocio.png.</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>Integrado; armonización visual y revisión humana pendientes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="108" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Explicitar el aporte de la arquitectura lógica a la continuidad del negocio y de las TIC.</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Bases Técnicas Transversales RT-10.03/04; ISO 22301:2019 e ISO/IEC 27031:2025.</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Subdoc 4.1: patrones de diseño y continuidad</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>Se incorporó el vínculo entre normas, funciones offline, dependencias, recuperación y reconciliación. Se definieron pruebas y la remisión al Subdoc 11 para BIA, activación y procedimientos; no se afirma certificación.</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>4.1, Patrones de diseño y continuidad; Referencias. https://www.iso.org/standard/75106.html ; https://www.iso.org/standard/27031</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Diseño documentado; pruebas y revisión humana pendientes</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="Rc4877283625f4917"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rb8f08f3eb8e1460e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="Raec8ab711cc3469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rad8b71f4dba64ee9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1198,6 +1198,32 @@
         <x:v>Diseño documentado; pruebas y revisión humana pendientes</x:v>
       </x:c>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Presentar primero la vista general completa y después la síntesis de la arquitectura lógica.</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Solicitud de Álvaro, 27-09-2026.</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Subdoc 4.1: capas de arquitectura</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>Se incorporó ARQL-01 de Tomás como primera figura y se mantuvo ARQL-19 a continuación, en páginas independientes, con referencias y pies actualizados.</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>4.1, Figuras 4.1 y 4.2.</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Implementado; revisión humana del consolidado pendiente</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observaciones Informe 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1289,6 +1289,132 @@
       <c r="H22" t="inlineStr">
         <is>
           <t>Resuelta</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>La vista general mostraba dos zonas, pero el texto declaraba un segundo lector Aurora en una tercera zona no dibujada; se requiere consistencia entre figura y arquitectura física.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Revisión del Informe 1, Subdocumento 4.2 (coherencia texto-diagrama); aclaración de LafroX del 26-09-2026; BTT RT-03.02.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 y 4.3 (LaTeX)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Se conserva la figura de dos zonas y se fija Aurora con escritor en sa-east-1a y lector promovible en sa-east-1b. RT-03.02 exige al menos dos zonas. Se alinean la introducción, el data center primario, el despliegue y ADR-12. Starlink queda solo en los tres cross-docking, conforme al T-11 y ADR-02.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>02_0_arquitectura_fisica.tex (texto posterior a Figura 1); 05_d_sitio_principal.tex (región y zonas); 11_j_despliegue.tex (alta disponibilidad); 14_m_decisiones_adr.tex (ADR-12)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>El LaTeX extendía AWS DMS CDC desde VM-02 de Talca a las cinco bases locales, aunque la arquitectura de integración (INT-12/C2) y la rama origin/arquitectura-alvaro lo especifican para VM-02 → Aurora.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Revisión de concordancia del Subdocumento 4; aclaración de LafroX del 26-09-2026; Arquitectura de Integración v01, INT-12/C2.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2, 4.3 y Formulario T-11</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Se mantiene AWS DMS CDC para replicar PostgreSQL de Talca (VM-02) al esquema de solo lectura en Aurora. Se elimina la afirmación de que DMS replica VM-C02 y los tres E-01; Concepción y los cross-docking sincronizan sus eventos mediante brokers y SQS FIFO. Se delimita el alcance en la introducción, el emplazamiento, la recuperación, el despliegue, ADR-09 y T-11. La continuidad Talca→Concepción y el RPO durante un corte total de enlaces requieren una decisión técnica separada.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>02_0_arquitectura_fisica.tex (introducción 4.2); 02_a_emplazamiento.tex (componentes híbridos); 02_c_conexiones.tex (corte VPN 4.2.5); 06_e_sitio_secundario.tex (replicación 4.3.2); 11_j_despliegue.tex (DR y reconciliación 4.2.4); 14_m_decisiones_adr.tex (ADR-09); 15_anexo_t11.tex (A-02)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>La figura general de arquitectura física requería una explicación separada por dominio antes del detalle técnico, manteniendo el título obligatorio 4.2.1 para implementos.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Solicitud de LafroX del 26-09-2026; aclaraciones de la licitación, sección 11, índice obligatorio 4.2/4.2.1.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 (LaTeX)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Se organiza la lectura posterior a la figura en dos vistas generales sin numeración: nube pública e instalaciones. Se agrupan el acceso, los servicios y la recuperación en nube, y se presenta la operación local, los enlaces y la sincronización de los sitios antes del detalle de 4.2.1 a 4.2.6. Se conserva 4.2.1 como Especificaciones Implementos a proveer.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>02_0_arquitectura_fisica.tex (texto posterior a la Figura 1, introducción de 4.2)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Atendida</t>
         </is>
       </c>
     </row>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="Raec8ab711cc3469e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rad8b71f4dba64ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R006e3f86ee334562"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R1cb70db3a6464251"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1203,16 +1203,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>Presentar primero la vista general completa y después la síntesis de la arquitectura lógica.</x:v>
+        <x:v>Presentar primero la vista general completa y después la síntesis, con una descripción propia para cada diagrama.</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Solicitud de Álvaro, 27-09-2026.</x:v>
+        <x:v>Solicitudes de Álvaro, 27 y 28-09-2026.</x:v>
       </x:c>
       <x:c r="D28" t="str">
         <x:v>Subdoc 4.1: capas de arquitectura</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>Se incorporó ARQL-01 de Tomás como primera figura y se mantuvo ARQL-19 a continuación, en páginas independientes, con referencias y pies actualizados.</x:v>
+        <x:v>Se incorporó ARQL-01 de Tomás antes de ARQL-19. Cada figura incluye su descripción y guía de lectura; se ajustó el tamaño de la síntesis para compartir página con su explicación.</x:v>
       </x:c>
       <x:c r="F28" t="str">
         <x:v>4.1, Figuras 4.1 y 4.2.</x:v>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Observaciones Informe 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1413,6 +1413,426 @@
         </is>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Lambda figuraba en la ingesta IoT, en los servicios contratados, en el T-11 y en el dimensionamiento del peak (100→500 concurrencias), pero ninguna función vigente la requiere: la excursión térmica se decide en el borde con Greengrass y los DTE los emite el ERP.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Revisión de concordancia del Subdocumento 4 solicitada por LafroX el 29-09-2026; coherencia entre catálogo de nodos, dimensionamiento y ADR-12.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2, 4.3 y Formulario T-11</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Se elimina AWS Lambda de la arquitectura física. IoT Core, con su motor de reglas, escribe las lecturas en DynamoDB y publica en SNS las que superan el umbral. La prueba de restauración mensual se realiza con AWS Backup. Se retira Lambda de la tabla de servicios, del T-11 (N-08), de ADR-12 y del dimensionamiento del peak.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>02_0_arquitectura_fisica.tex (introducción 4.2); 02_a_emplazamiento.tex (N-08); 02_b_servicios_nube.tex (tabla de servicios); 14_m_decisiones_adr.tex (ADR-12); 15_anexo_t11.tex (N-08); 4.3 completo sin imagenes_v2.md; entrega_2/arquitectura_fisica.md (Tabla 82, escalado, ADR-12, respaldo y plan de capacidad)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>La puerta de enlace no podía autenticar tokens de Keycloak en API REST y las consolas internas no tenían puerta propia.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Revisión de cumplimiento de Bases del Subdocumento 4 solicitada por LafroX el 29-09-2026. BTT RT-11.11.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 y Formulario T-11</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>API Gateway con dos API REST: pública solo invocable por CloudFront (encabezado de origen y endpoint predeterminado deshabilitado) y privada por endpoint de VPC; autorizador Lambda único para los JWT de Keycloak; se reemplaza ADR-13.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>14_m_decisiones_adr.tex (ADR-13); 02_b_servicios_nube.tex; 15_anexo_t11.tex</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Faltaba el acceso remoto de confianza cero con postura y la ruta autorizada de oficina y back-office que la 4.1 delega en la 4.2.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Revisión de cumplimiento de Bases del Subdocumento 4 solicitada por LafroX el 29-09-2026. BTT RT-03.22, RT-11.01, RT-12.03; 4.1 lógica.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 y Formulario T-11</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS Verified Access para oficina y trabajo remoto con Keycloak (MFA) y CrowdStrike Falcon como proveedor de postura; frontend de consolas tras ALB privado hacia la API privada; nuevo ADR-16; estaciones existentes bajo gestión central.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>14_m_decisiones_adr.tex (ADR-16); 02_c_conexiones.tex; 02_a_emplazamiento.tex (N-04, N-12); 04_c_implementos.tex; 15_anexo_t11.tex</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>El transporte AS2 con AWS Transfer Family recibía por HTTP en TCP 5080 y no cumplía TLS 1.3 en tránsito.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Revisión de cumplimiento de Bases del Subdocumento 4 solicitada por LafroX el 29-09-2026. BTT RT-11.08, RT-03.05, RT-05.23.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 y Formulario T-11</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Transporte AS2 con OpenAS2 en contenedor propio en Fargate tras Network Load Balancer con paso TLS directo; lista de IP por cadena, firma, cifrado y MDN; ADR-11 conserva alternativas e hito de enero de 2029.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>14_m_decisiones_adr.tex (ADR-11); 02_a_emplazamiento.tex; 02_b_servicios_nube.tex; 11_j_despliegue.tex; 15_anexo_t11.tex</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>No se declaraba la superficie de exposición, el terreno entraba directo a API Gateway y el ALB figuraba en subred pública.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Revisión de cumplimiento de Bases del Subdocumento 4 solicitada por LafroX el 29-09-2026. BTT RT-11.07, RT-11.13; 4.1 lógica (CloudFront entrada única).</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Nueva subsección Superficie de exposición; terreno por CloudFront (/v1 y /sync/v1); ALB privados y subred pública solo con NAT y NLB de AS2; filas de oficina y AS2 en la tabla de conexiones.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>02_c_conexiones.tex (tablas de conexiones y superficie, figura); 11_j_despliegue.tex (tabla de direccionamiento); 02_0_arquitectura_fisica.tex</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Acceso privilegiado, cuenta de último recurso, BI de autoservicio, continuidad de la oficina y pruebas de carga sin cobertura suficiente.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Revisión de cumplimiento de Bases del Subdocumento 4 solicitada por LafroX el 29-09-2026. BTT RT-11.27, RT-12.06, RT-12.13, RT-05.27, RT-14.02, RT-10.02-10.07, RT-09.06, RT-08.07-08.09.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2, 4.3 y Formulario T-11</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Identity Center federado con permisos temporales y sesiones registradas; procedimiento de cuenta de emergencia; QuickSight embebido con autoservicio; falla del enlace de Talca para la oficina; pruebas con oficina y remoto; especificación de estaciones.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>11_j_despliegue.tex (ambientes, verificación); 02_a_emplazamiento.tex (N-10); 02_c_conexiones.tex (fallas); 12_k_dimensionamiento.tex; 15_anexo_t11.tex</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Recuperación ante desastres duplicada entre 4.2.4 y 4.3.2 y conmutación basada solo en DNS; títulos de 4.3 no literales al índice.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Revisión de cumplimiento de Bases del Subdocumento 4 solicitada por LafroX el 29-09-2026. Aclaraciones, sección 11 (Capítulo 4) y sección 2; BTT RT-07.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2 y 4.3</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>El procedimiento de conmutación queda solo en 4.3.2 con restitución de identidad, API y consolas y validación con escrituras; 4.2.4 resume y referencia; títulos 4.3, 4.3.1 y 4.3.2 literales; cifra IoT corregida a 12.600.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>06_e_sitio_secundario.tex; 11_j_despliegue.tex (recuperación ante desastres); 05_d_sitio_principal.tex (títulos); 02_a_emplazamiento.tex (N-08)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Párrafos densos con enumeraciones y oraciones mal construidas dificultaban la lectura del Subdocumento 4.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Solicitud de LafroX del 29-09-2026; aclaraciones de la licitación, secciones 3 y 5 (redacción y legibilidad).</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2, 4.3 y Anexo 4.B</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Se convirtieron en listas con frase introductoria las enumeraciones, secuencias y criterios, y se corrigió la gramática de 4.3; se verificó que ninguna cifra, código, referencia ni nombre se perdiera.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>02_0, 04_c, 02_a, 02_b, 11_j, 02_c, 12_k, 05_d, 06_e, 14_m y 16_anexo_4b (sin cambios de contenido)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Afirmaciones sin sustento o contradictorias en el Subdocumento 4 (retorno automático de DR, tiempos de conmutación, RTO 24-72 h, 105 TPS, puntos únicos de falla, conductores, transferencia por Internet, ISO 27017/27018, portabilidad).</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Solicitud de LafroX del 29-09-2026 (auditoría de afirmaciones, tanda A); aclaraciones, indicadores de IA por contradicción.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2, 4.3 y ADR</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Se eliminaron o acotaron las afirmaciones sin respaldo y se alinearon las contradicciones: retorno regional coordinado, tiempos de AWS como objetivos medidos, recuperación en frío cualitativa, S3 RTC al 99,99 %, dotación de conductores y referencias a la arquitectura de seguridad.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>02_a, 02_b, 02_c, 04_c, 05_d, 06_e, 11_j, 14_m y 15_anexo_t11</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Atendida</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Incoherencias internas del Subdocumento 4.2 y con el Subdocumento 4.1 (texto repetido, cifras distintas, terminología de la cuenta de emergencia, detalle del manifiesto de turno, prueba de pérdida de sitio).</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Solicitud de LafroX del 29-09-2026 (revisión de coherencia 4.1-4.2).</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Subdoc 4.2, 4.3, ADR y T-11</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Se dejó una sola explicación de las capacidades excluidas de us-east-1, se retiró la cifra de 105 TPS, se unificó "cuenta de último recurso", se agregó a ADR-06 la ventana de 26 h del manifiesto, se agregó la prueba de pérdida del sitio de Talca, se declaró RAID 10/6 con referencia a ADR-10, se corrigió la cobertura Wi-Fi a 144 terminales y se corrigió redacción de 4.3.2.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>02_b, 02_c, 05_d, 06_e, 11_j, 14_m y 15_anexo_t11</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>LafroX</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>Atendida</t>
         </is>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R006e3f86ee334562"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R1cb70db3a6464251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R406c256d1ac347b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R4650b984a0c44c78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1224,6 +1224,162 @@
         <x:v>Implementado; revisión humana del consolidado pendiente</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" ht="150" customHeight="1">
+      <x:c r="A29" s="3" t="str">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B29" s="3" t="str">
+        <x:v>Unificar las fuentes lógicas Laravel y corregir contradicciones de continuidad.</x:v>
+      </x:c>
+      <x:c r="C29" s="3" t="str">
+        <x:v>Auditoría comunicada por Álvaro, 29-09-2026; Aclaraciones §§3 y 7.1.</x:v>
+      </x:c>
+      <x:c r="D29" s="3" t="str">
+        <x:v>4.1 y Markdown lógico</x:v>
+      </x:c>
+      <x:c r="E29" s="3" t="str">
+        <x:v>Se sincronizan tecnologías, exposición, separación OpenAS2/M11 y CDC exclusivo de Talca. No se modifica 4.2.</x:v>
+      </x:c>
+      <x:c r="F29" s="3" t="str">
+        <x:v>Capas 2, 4, 6, 7; catálogo; texto lógico.</x:v>
+      </x:c>
+      <x:c r="G29" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H29" s="3" t="str">
+        <x:v>Implementado en lógica; coherencia integrada requiere consolidar 4.2.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="150" customHeight="1">
+      <x:c r="A30" s="3" t="str">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B30" s="3" t="str">
+        <x:v>Resolver despacho de 96 camiones ante falla ERP/DTE.</x:v>
+      </x:c>
+      <x:c r="C30" s="3" t="str">
+        <x:v>Caso 02, ventana 05:30–07:00; observación prioritaria 2.</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="str">
+        <x:v>4.1 POD–DTE–acuse</x:v>
+      </x:c>
+      <x:c r="E30" s="3" t="str">
+        <x:v>Se definen estados, consulta idempotente y control de liberación. AL-DTE-01 exige procedimiento del CLIENTE y ensayo de 96 salidas.</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="str">
+        <x:v>4.1 control de liberación; Anexo M, AL-DTE-01.</x:v>
+      </x:c>
+      <x:c r="G30" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="str">
+        <x:v>Diseño y protocolo definidos; aprobación tributaria y ensayo no acreditados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="150" customHeight="1">
+      <x:c r="A31" s="3" t="str">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B31" s="3" t="str">
+        <x:v>Demostrar RPO15 con pérdida de sitio y WAN; probar autonomía con dos relevos.</x:v>
+      </x:c>
+      <x:c r="C31" s="3" t="str">
+        <x:v>RT-07.04; RT-03.10/13; observaciones 3 y 5.</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="str">
+        <x:v>4.1 continuidad y funciones offline</x:v>
+      </x:c>
+      <x:c r="E31" s="3" t="str">
+        <x:v>Se retira garantía incondicional sin sustento. AL-DR-01 y AL-OFF-01 definen medición y aceptación; AL-BR-01 registra brecha.</x:v>
+      </x:c>
+      <x:c r="F31" s="3" t="str">
+        <x:v>Anexo M; reconciliación y condiciones de diseño.</x:v>
+      </x:c>
+      <x:c r="G31" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H31" s="3" t="str">
+        <x:v>Pruebas no ejecutadas. Protección externa bajo aislamiento no resuelta.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="150" customHeight="1">
+      <x:c r="A32" s="3" t="str">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B32" s="3" t="str">
+        <x:v>Completar modo, volumen, disponibilidad y conducta de cada integración.</x:v>
+      </x:c>
+      <x:c r="C32" s="3" t="str">
+        <x:v>RT-05.21; observación prioritaria 4.</x:v>
+      </x:c>
+      <x:c r="D32" s="3" t="str">
+        <x:v>4.1 catálogo y anexos G–I</x:v>
+      </x:c>
+      <x:c r="E32" s="3" t="str">
+        <x:v>Quince fichas con unidades, fórmulas, ventanas requeridas y conducta ante lentitud/error. Se elimina total agregado que mezclaba unidades y dobles conteos.</x:v>
+      </x:c>
+      <x:c r="F32" s="3" t="str">
+        <x:v>Anexos G, H e I.</x:v>
+      </x:c>
+      <x:c r="G32" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H32" s="3" t="str">
+        <x:v>Catálogo documental ampliado; SLA de terceros y supuestos requieren contrato/medición.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="150" customHeight="1">
+      <x:c r="A33" s="3" t="str">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B33" s="3" t="str">
+        <x:v>Verificar correspondencia completa capítulo 3–lógica–física.</x:v>
+      </x:c>
+      <x:c r="C33" s="3" t="str">
+        <x:v>Aclaraciones capítulo 4; observación 6.</x:v>
+      </x:c>
+      <x:c r="D33" s="3" t="str">
+        <x:v>4.1 relación de vistas</x:v>
+      </x:c>
+      <x:c r="E33" s="3" t="str">
+        <x:v>Anexo N cubre 12 módulos y servicios transversales, señala numeración desactualizada del capítulo 3 y criterio AL-MAP-01.</x:v>
+      </x:c>
+      <x:c r="F33" s="3" t="str">
+        <x:v>Anexo N, tabla de correspondencia.</x:v>
+      </x:c>
+      <x:c r="G33" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H33" s="3" t="str">
+        <x:v>12/12 módulos identificados; no equivale al 100% del inventario integrado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="150" customHeight="1">
+      <x:c r="A34" s="3" t="str">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B34" s="3" t="str">
+        <x:v>Ajustar identificación de entrega y declarar asistencia IA; revisar figuras.</x:v>
+      </x:c>
+      <x:c r="C34" s="3" t="str">
+        <x:v>Aclaraciones §§1, 4 y 7.2; observaciones 7 y 8.</x:v>
+      </x:c>
+      <x:c r="D34" s="3" t="str">
+        <x:v>Portada lógica, cierre 4.1 y anexos</x:v>
+      </x:c>
+      <x:c r="E34" s="3" t="str">
+        <x:v>Portada Entrega 2 y declaración de IA con revisión humana aún no realizada. Se preserva la vista de Tomás; quedan diferencias visuales inventariadas.</x:v>
+      </x:c>
+      <x:c r="F34" s="3" t="str">
+        <x:v>main.tex; declaraciones finales; README del 4.1.</x:v>
+      </x:c>
+      <x:c r="G34" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H34" s="3" t="str">
+        <x:v>Formato parcial corregido. Faltan figuras definitivas, revisión humana y capítulo 4 integrado.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R406c256d1ac347b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R4650b984a0c44c78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="Rd633fa01ff8342f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R3aaca41890c9411c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1380,6 +1380,32 @@
         <x:v>Formato parcial corregido. Faltan figuras definitivas, revisión humana y capítulo 4 integrado.</x:v>
       </x:c>
     </x:row>
+    <x:row r="35" ht="150" customHeight="1">
+      <x:c r="A35" s="3" t="str">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B35" s="3" t="str">
+        <x:v>Organizar el apartado lógico por archivos editables, siguiendo la estructura modular de 4.2.</x:v>
+      </x:c>
+      <x:c r="C35" s="3" t="str">
+        <x:v>Solicitud de Álvaro, 30-09-2026.</x:v>
+      </x:c>
+      <x:c r="D35" s="3" t="str">
+        <x:v>Organización de 4.1 y paquete de distribución</x:v>
+      </x:c>
+      <x:c r="E35" s="3" t="str">
+        <x:v>Se separan 24 fragmentos del cuerpo y 17 de anexos. Se conservan las entradas de compilación y se adapta el exportador.</x:v>
+      </x:c>
+      <x:c r="F35" s="3" t="str">
+        <x:v>Concatenación exacta de fuentes y texto idéntico por página. PDF principal: 60 páginas; anexos: 28.</x:v>
+      </x:c>
+      <x:c r="G35" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H35" s="3" t="str">
+        <x:v>Reorganización implementada sin cambios técnicos ni de arquitectura física. No cierra las brechas de aceptación pendientes.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="Rd633fa01ff8342f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R3aaca41890c9411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R69a2350842444ecc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R966ddb3e832f4b33"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1406,6 +1406,214 @@
         <x:v>Reorganización implementada sin cambios técnicos ni de arquitectura física. No cierra las brechas de aceptación pendientes.</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" ht="150" customHeight="1">
+      <x:c r="A36" s="3" t="str">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B36" s="3" t="str">
+        <x:v>Catálogo completo y navegación de anexos</x:v>
+      </x:c>
+      <x:c r="C36" s="3" t="str">
+        <x:v>Plan de mejora aceptado por Álvaro; aclaraciones y bases.</x:v>
+      </x:c>
+      <x:c r="D36" s="3" t="str">
+        <x:v>Arquitectura lógica 4.1</x:v>
+      </x:c>
+      <x:c r="E36" s="3" t="str">
+        <x:v>22 anexos A–V con enlaces, páginas e identificadores de requisito.</x:v>
+      </x:c>
+      <x:c r="F36" s="3" t="str">
+        <x:v>Fuentes, catálogo de anexos y compilación de distribución.</x:v>
+      </x:c>
+      <x:c r="G36" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H36" s="3" t="str">
+        <x:v>Implementación documental; no acredita aprobación del CLIENTE ni ensayos ejecutados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="150" customHeight="1">
+      <x:c r="A37" s="3" t="str">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B37" s="3" t="str">
+        <x:v>Correspondencia lógica</x:v>
+      </x:c>
+      <x:c r="C37" s="3" t="str">
+        <x:v>Plan de mejora aceptado por Álvaro; aclaraciones y bases.</x:v>
+      </x:c>
+      <x:c r="D37" s="3" t="str">
+        <x:v>Arquitectura lógica 4.1</x:v>
+      </x:c>
+      <x:c r="E37" s="3" t="str">
+        <x:v>49 unidades: 12 módulos y 37 capacidades transversales; el cierre integrado exige enlaces físicos exactos.</x:v>
+      </x:c>
+      <x:c r="F37" s="3" t="str">
+        <x:v>Fuentes, catálogo de anexos y compilación de distribución.</x:v>
+      </x:c>
+      <x:c r="G37" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H37" s="3" t="str">
+        <x:v>Implementación documental; no acredita aprobación del CLIENTE ni ensayos ejecutados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="150" customHeight="1">
+      <x:c r="A38" s="3" t="str">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B38" s="3" t="str">
+        <x:v>Decisiones verificables</x:v>
+      </x:c>
+      <x:c r="C38" s="3" t="str">
+        <x:v>Plan de mejora aceptado por Álvaro; aclaraciones y bases.</x:v>
+      </x:c>
+      <x:c r="D38" s="3" t="str">
+        <x:v>Arquitectura lógica 4.1</x:v>
+      </x:c>
+      <x:c r="E38" s="3" t="str">
+        <x:v>Anexo O con ADR fechados, alternativas, criterios y ensayos; REST API / REQUEST / VPC Link V2 hacia ALB.</x:v>
+      </x:c>
+      <x:c r="F38" s="3" t="str">
+        <x:v>Fuentes, catálogo de anexos y compilación de distribución.</x:v>
+      </x:c>
+      <x:c r="G38" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H38" s="3" t="str">
+        <x:v>Implementación documental; no acredita aprobación del CLIENTE ni ensayos ejecutados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="150" customHeight="1">
+      <x:c r="A39" s="3" t="str">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B39" s="3" t="str">
+        <x:v>Tecnologías y soporte</x:v>
+      </x:c>
+      <x:c r="C39" s="3" t="str">
+        <x:v>Plan de mejora aceptado por Álvaro; aclaraciones y bases.</x:v>
+      </x:c>
+      <x:c r="D39" s="3" t="str">
+        <x:v>Arquitectura lógica 4.1</x:v>
+      </x:c>
+      <x:c r="E39" s="3" t="str">
+        <x:v>Anexo P con soporte y actualizaciones durante 56 meses; Terraform propietario y Ansible para hosts.</x:v>
+      </x:c>
+      <x:c r="F39" s="3" t="str">
+        <x:v>Fuentes, catálogo de anexos y compilación de distribución.</x:v>
+      </x:c>
+      <x:c r="G39" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H39" s="3" t="str">
+        <x:v>Implementación documental; no acredita aprobación del CLIENTE ni ensayos ejecutados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="150" customHeight="1">
+      <x:c r="A40" s="3" t="str">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B40" s="3" t="str">
+        <x:v>Seguridad lógica</x:v>
+      </x:c>
+      <x:c r="C40" s="3" t="str">
+        <x:v>Plan de mejora aceptado por Álvaro; aclaraciones y bases.</x:v>
+      </x:c>
+      <x:c r="D40" s="3" t="str">
+        <x:v>Arquitectura lógica 4.1</x:v>
+      </x:c>
+      <x:c r="E40" s="3" t="str">
+        <x:v>Anexos Q/R: STRIDE por módulo y frontera, controles ISO y evidencia requerida; no declara certificación.</x:v>
+      </x:c>
+      <x:c r="F40" s="3" t="str">
+        <x:v>Fuentes, catálogo de anexos y compilación de distribución.</x:v>
+      </x:c>
+      <x:c r="G40" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H40" s="3" t="str">
+        <x:v>Implementación documental; no acredita aprobación del CLIENTE ni ensayos ejecutados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="150" customHeight="1">
+      <x:c r="A41" s="3" t="str">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B41" s="3" t="str">
+        <x:v>Desempeño y evidencia documental</x:v>
+      </x:c>
+      <x:c r="C41" s="3" t="str">
+        <x:v>Plan de mejora aceptado por Álvaro; aclaraciones y bases.</x:v>
+      </x:c>
+      <x:c r="D41" s="3" t="str">
+        <x:v>Arquitectura lógica 4.1</x:v>
+      </x:c>
+      <x:c r="E41" s="3" t="str">
+        <x:v>Anexos T/U: percentiles, cargas de 1,5 peak y crecimiento tres veces; POD distinto de acuse tributario.</x:v>
+      </x:c>
+      <x:c r="F41" s="3" t="str">
+        <x:v>Fuentes, catálogo de anexos y compilación de distribución.</x:v>
+      </x:c>
+      <x:c r="G41" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H41" s="3" t="str">
+        <x:v>Implementación documental; no acredita aprobación del CLIENTE ni ensayos ejecutados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="150" customHeight="1">
+      <x:c r="A42" s="3" t="str">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B42" s="3" t="str">
+        <x:v>Alcance y condiciones de aceptación</x:v>
+      </x:c>
+      <x:c r="C42" s="3" t="str">
+        <x:v>Plan de mejora aceptado por Álvaro; aclaraciones y bases.</x:v>
+      </x:c>
+      <x:c r="D42" s="3" t="str">
+        <x:v>Arquitectura lógica 4.1</x:v>
+      </x:c>
+      <x:c r="E42" s="3" t="str">
+        <x:v>M10/M12 en Etapa 2; Anexo V mantiene decisiones del CLIENTE, ensayos y revisión humana como pendientes.</x:v>
+      </x:c>
+      <x:c r="F42" s="3" t="str">
+        <x:v>Fuentes, catálogo de anexos y compilación de distribución.</x:v>
+      </x:c>
+      <x:c r="G42" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H42" s="3" t="str">
+        <x:v>Implementación documental; no acredita aprobación del CLIENTE ni ensayos ejecutados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="150" customHeight="1">
+      <x:c r="A43" s="3" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B43" s="3" t="str">
+        <x:v>Consistencia editorial y figuras</x:v>
+      </x:c>
+      <x:c r="C43" s="3" t="str">
+        <x:v>Plan de mejora aceptado por Álvaro; aclaraciones y bases.</x:v>
+      </x:c>
+      <x:c r="D43" s="3" t="str">
+        <x:v>Arquitectura lógica 4.1</x:v>
+      </x:c>
+      <x:c r="E43" s="3" t="str">
+        <x:v>Referencias técnicas, ADR sin tabla partida y general consolidada del modelo de Tomás; original preservado.</x:v>
+      </x:c>
+      <x:c r="F43" s="3" t="str">
+        <x:v>Fuentes, catálogo de anexos y compilación de distribución.</x:v>
+      </x:c>
+      <x:c r="G43" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H43" s="3" t="str">
+        <x:v>Implementación documental; no acredita aprobación del CLIENTE ni ensayos ejecutados.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
+++ b/00_trazabilidad_observaciones/tablas/Trazabilidad_Observaciones_Informe1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="R69a2350842444ecc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R966ddb3e832f4b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observaciones Informe 1" sheetId="1" r:id="Rd5a26a8d233c4dfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="Rdad77932218f4915"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1614,6 +1614,84 @@
         <x:v>Implementación documental; no acredita aprobación del CLIENTE ni ensayos ejecutados.</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" ht="150" customHeight="1">
+      <x:c r="A44" s="3" t="str">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B44" s="3" t="str">
+        <x:v>Restaurar el diagrama general anterior de arquitectura lógica.</x:v>
+      </x:c>
+      <x:c r="C44" s="3" t="str">
+        <x:v>Solicitud de Álvaro, 30-09-2026.</x:v>
+      </x:c>
+      <x:c r="D44" s="3" t="str">
+        <x:v>4.1.3 Capas de la arquitectura, Figura 4.1</x:v>
+      </x:c>
+      <x:c r="E44" s="3" t="str">
+        <x:v>Se restaura ARQL-01_Vision_general.png de Tomás y se retira la vista consolidada añadida. Se conservan la síntesis de ocho capas y los anexos.</x:v>
+      </x:c>
+      <x:c r="F44" s="3" t="str">
+        <x:v>Referencia LaTeX y Markdown, compilación y distribución autocontenida.</x:v>
+      </x:c>
+      <x:c r="G44" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H44" s="3" t="str">
+        <x:v>Cambio visual solicitado; no modifica decisiones de diseño ni arquitectura física.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="180" customHeight="1">
+      <x:c r="A45" s="3" t="str">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B45" s="3" t="str">
+        <x:v>Incorporar detalle visual de cada una de las ocho capas después de la vista resumida.</x:v>
+      </x:c>
+      <x:c r="C45" s="3" t="str">
+        <x:v>Solicitud y aprobación de Álvaro, 01-10-2026; Aclaraciones, reglas de diagramas.</x:v>
+      </x:c>
+      <x:c r="D45" s="3" t="str">
+        <x:v>4.1.3 Capas de la arquitectura, apartados 1–8</x:v>
+      </x:c>
+      <x:c r="E45" s="3" t="str">
+        <x:v>Se incorporan ocho diagramas independientes basados en la vista de Tomás y coherentes con los contratos vigentes; cada figura se cita, identifica su fuente y se explica. Se conservan las dos vistas iniciales.</x:v>
+      </x:c>
+      <x:c r="F45" s="3" t="str">
+        <x:v>Fuentes editables, legibilidad impresa, referencias y compilación LuaLaTeX.</x:v>
+      </x:c>
+      <x:c r="G45" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H45" s="3" t="str">
+        <x:v>Cambio de presentación de la arquitectura lógica. No modifica la física ni acredita ensayos operativos.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="180" customHeight="1">
+      <x:c r="A46" s="3" t="str">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B46" s="3" t="str">
+        <x:v>Sustituir las propuestas de detalle por los recortes de Tomás mostrados en la vista preliminar.</x:v>
+      </x:c>
+      <x:c r="C46" s="3" t="str">
+        <x:v>Corrección explícita de Álvaro, 01-10-2026.</x:v>
+      </x:c>
+      <x:c r="D46" s="3" t="str">
+        <x:v>4.1.3 Capas de la arquitectura, apartados 1–8</x:v>
+      </x:c>
+      <x:c r="E46" s="3" t="str">
+        <x:v>Se retiran las ocho propuestas añadidas y se usan los ocho recortes originales, sin redibujar, recolorear ni cambiar etiquetas. Se conservan la vista general, la síntesis y las explicaciones técnicas.</x:v>
+      </x:c>
+      <x:c r="F46" s="3" t="str">
+        <x:v>Coordenadas de la vista preliminar, igualdad de píxeles, fuentes, referencias y compilación LuaLaTeX.</x:v>
+      </x:c>
+      <x:c r="G46" s="3" t="str">
+        <x:v>LafroX</x:v>
+      </x:c>
+      <x:c r="H46" s="3" t="str">
+        <x:v>Aplicación por instrucción expresa. Las Aclaraciones prohíben recortes como figuras de detalle; no se declara conformidad con esa regla ni se corrigen las etiquetas heredadas.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
